--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N55_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N55_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>32.53207106775812</v>
+        <v>5.286461548510696</v>
       </c>
       <c r="D2" t="n">
-        <v>32.53167606709875</v>
+        <v>5.286397360903547</v>
       </c>
       <c r="E2" t="n">
-        <v>11.25643522417689</v>
+        <v>1.829170723928745</v>
       </c>
       <c r="F2" t="n">
-        <v>11.24662813168766</v>
+        <v>1.827577071399245</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.73795222414611</v>
+        <v>5.482417236423744</v>
       </c>
       <c r="D3" t="n">
-        <v>33.72963318661965</v>
+        <v>5.481065392825694</v>
       </c>
       <c r="E3" t="n">
-        <v>11.25643522417689</v>
+        <v>1.829170723928745</v>
       </c>
       <c r="F3" t="n">
-        <v>11.24662813168766</v>
+        <v>1.827577071399245</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>6.194100033361516</v>
+        <v>1.006541255421246</v>
       </c>
       <c r="D4" t="n">
-        <v>6.239891351278128</v>
+        <v>1.013982344582696</v>
       </c>
       <c r="E4" t="n">
-        <v>11.25643522417689</v>
+        <v>1.829170723928745</v>
       </c>
       <c r="F4" t="n">
-        <v>11.24662813168766</v>
+        <v>1.827577071399245</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.01746598005876</v>
+        <v>5.690338221759548</v>
       </c>
       <c r="D5" t="n">
-        <v>35.01131350839366</v>
+        <v>5.689338445113969</v>
       </c>
       <c r="E5" t="n">
-        <v>11.25643522417689</v>
+        <v>1.829170723928745</v>
       </c>
       <c r="F5" t="n">
-        <v>11.24662813168766</v>
+        <v>1.827577071399245</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.56197461096215</v>
+        <v>5.778820874281349</v>
       </c>
       <c r="D6" t="n">
-        <v>35.64183023699209</v>
+        <v>5.791797413511215</v>
       </c>
       <c r="E6" t="n">
-        <v>11.25643522417689</v>
+        <v>1.829170723928745</v>
       </c>
       <c r="F6" t="n">
-        <v>11.24662813168766</v>
+        <v>1.827577071399245</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
